--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,48 +1603,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137101121</v>
+        <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92139</v>
+        <v>92529</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramsdal, Ög</t>
+          <t>Hultbacken NNV 310 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607017</v>
+        <v>607104</v>
       </c>
       <c r="R11" t="n">
-        <v>6484514</v>
+        <v>6484384</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1682,30 +1693,41 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallskog med inslag av gran</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Jan-Erik Axelsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137101121</t>
+          <t>https://artportalen.se/Sighting/137119497</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137101232</v>
+        <v>137101121</v>
       </c>
       <c r="B12" t="n">
         <v>92139</v>
@@ -1740,13 +1762,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607065</v>
+        <v>607017</v>
       </c>
       <c r="R12" t="n">
-        <v>6484477</v>
+        <v>6484514</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1801,13 +1823,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137101232</t>
+          <t>https://artportalen.se/Sighting/137101121</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137101624</v>
+        <v>137101232</v>
       </c>
       <c r="B13" t="n">
         <v>92139</v>
@@ -1838,17 +1860,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hultbacken, Ög</t>
+          <t>Ramsdal, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607185</v>
+        <v>607065</v>
       </c>
       <c r="R13" t="n">
-        <v>6484350</v>
+        <v>6484477</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1903,16 +1925,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137101624</t>
+          <t>https://artportalen.se/Sighting/137101232</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137101158</v>
+        <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>93454</v>
+        <v>92139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,34 +1942,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramsdal, Ög</t>
+          <t>Hultbacken, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607014</v>
+        <v>607185</v>
       </c>
       <c r="R14" t="n">
-        <v>6484497</v>
+        <v>6484350</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2005,16 +2027,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137101158</t>
+          <t>https://artportalen.se/Sighting/137101624</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137102567</v>
+        <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>80102</v>
+        <v>93454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,37 +2044,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hultbacken, Ög</t>
+          <t>Ramsdal, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>606981</v>
+        <v>607014</v>
       </c>
       <c r="R15" t="n">
-        <v>6484189</v>
+        <v>6484497</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2107,62 +2129,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137102567</t>
+          <t>https://artportalen.se/Sighting/137101158</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137109598</v>
+        <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>58005</v>
+        <v>80102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hultbacken, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607137</v>
+        <v>606981</v>
       </c>
       <c r="R16" t="n">
-        <v>6483887</v>
+        <v>6484189</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2192,11 +2206,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska födosök i död stående gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2211,24 +2220,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109598</t>
+          <t>https://artportalen.se/Sighting/137102567</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137109858</v>
+        <v>137109598</v>
       </c>
       <c r="B17" t="n">
         <v>58005</v>
@@ -2271,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>606804</v>
+        <v>607137</v>
       </c>
       <c r="R17" t="n">
-        <v>6484296</v>
+        <v>6483887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,16 +2346,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109858</t>
+          <t>https://artportalen.se/Sighting/137109598</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137099467</v>
+        <v>137109858</v>
       </c>
       <c r="B18" t="n">
-        <v>5182</v>
+        <v>58005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,42 +2363,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergkärr, Ög</t>
+          <t>Hultbacken, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>606746</v>
+        <v>606804</v>
       </c>
       <c r="R18" t="n">
-        <v>6484301</v>
+        <v>6484296</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2419,6 +2431,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska födosök i död stående gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2433,27 +2450,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137099467</t>
+          <t>https://artportalen.se/Sighting/137109858</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137109552</v>
+        <v>137099467</v>
       </c>
       <c r="B19" t="n">
-        <v>58164</v>
+        <v>5182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,45 +2478,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103023</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hultbacken, Ög</t>
+          <t>Bergkärr, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>606887</v>
+        <v>606746</v>
       </c>
       <c r="R19" t="n">
-        <v>6483936</v>
+        <v>6484301</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2543,73 +2557,70 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109552</t>
+          <t>https://artportalen.se/Sighting/137099467</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137109567</v>
+        <v>137123825</v>
       </c>
       <c r="B20" t="n">
-        <v>58164</v>
+        <v>5181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103023</v>
+        <v>102204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hultbacken, Ög</t>
+          <t>Bergkärr, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607004</v>
+        <v>606931</v>
       </c>
       <c r="R20" t="n">
-        <v>6484489</v>
+        <v>6484081</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2653,27 +2664,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137109567</t>
+          <t>https://artportalen.se/Sighting/137123825</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137099977</v>
+        <v>137109552</v>
       </c>
       <c r="B21" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2681,37 +2692,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hemmingstorp, Ög</t>
+          <t>Hultbacken, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>606931</v>
+        <v>606887</v>
       </c>
       <c r="R21" t="n">
-        <v>6484415</v>
+        <v>6483936</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2755,27 +2774,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137099977</t>
+          <t>https://artportalen.se/Sighting/137109552</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137102178</v>
+        <v>137109567</v>
       </c>
       <c r="B22" t="n">
-        <v>8463</v>
+        <v>58164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2783,37 +2802,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hultbacken, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607096</v>
+        <v>607004</v>
       </c>
       <c r="R22" t="n">
-        <v>6484294</v>
+        <v>6484489</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2857,24 +2884,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137102178</t>
+          <t>https://artportalen.se/Sighting/137109567</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137103339</v>
+        <v>137099977</v>
       </c>
       <c r="B23" t="n">
         <v>8463</v>
@@ -2905,17 +2932,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hultbacken, Ög</t>
+          <t>Hemmingstorp, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607105</v>
+        <v>606931</v>
       </c>
       <c r="R23" t="n">
-        <v>6484021</v>
+        <v>6484415</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2970,13 +2997,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137103339</t>
+          <t>https://artportalen.se/Sighting/137099977</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137109991</v>
+        <v>137102178</v>
       </c>
       <c r="B24" t="n">
         <v>8463</v>
@@ -3005,25 +3032,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hultbacken, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>606988</v>
+        <v>607096</v>
       </c>
       <c r="R24" t="n">
-        <v>6484470</v>
+        <v>6484294</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3064,25 +3082,610 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137102178</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137103339</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hultbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>607105</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6484021</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137103339</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137109991</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hultbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>606988</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6484470</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137109991</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137119393</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99362</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hemmingstorp OSO 280 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>606926</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6484377</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137119393</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137119536</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99362</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hultbacken NNV 205 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>607153</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6484290</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137119536</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137119430</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106503</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hemmingstorp O 350 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>607002</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6484424</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jonsberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson, Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137119430</t>
         </is>
       </c>
     </row>
@@ -3111,6 +3714,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137109598</v>
       </c>
       <c r="B17" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>137109858</v>
       </c>
       <c r="B18" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>137109552</v>
       </c>
       <c r="B21" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>137109567</v>
       </c>
       <c r="B22" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137109598</v>
       </c>
       <c r="B17" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>137109858</v>
       </c>
       <c r="B18" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>137109552</v>
       </c>
       <c r="B21" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>137109567</v>
       </c>
       <c r="B22" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>137099977</v>
       </c>
       <c r="B23" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137102178</v>
       </c>
       <c r="B24" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>137103339</v>
       </c>
       <c r="B25" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>137109991</v>
       </c>
       <c r="B26" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -2268,11 +2268,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2383,11 +2379,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2496,11 +2488,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bergkärr, Ög</t>
@@ -2603,11 +2591,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bergkärr, Ög</t>
@@ -2712,11 +2696,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2822,11 +2802,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3239,11 +3215,7 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3357,11 +3329,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3481,11 +3449,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3605,11 +3569,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137109598</v>
       </c>
       <c r="B17" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137109858</v>
       </c>
       <c r="B18" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>137099467</v>
       </c>
       <c r="B19" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137123825</v>
       </c>
       <c r="B20" t="n">
-        <v>5181</v>
+        <v>5187</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137109552</v>
       </c>
       <c r="B21" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>137109567</v>
       </c>
       <c r="B22" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>137099977</v>
       </c>
       <c r="B23" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>137102178</v>
       </c>
       <c r="B24" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>137103339</v>
       </c>
       <c r="B25" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>137109991</v>
       </c>
       <c r="B26" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137109598</v>
       </c>
       <c r="B17" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137109858</v>
       </c>
       <c r="B18" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137109552</v>
       </c>
       <c r="B21" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>137109567</v>
       </c>
       <c r="B22" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137109598</v>
       </c>
       <c r="B17" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137109858</v>
       </c>
       <c r="B18" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137109552</v>
       </c>
       <c r="B21" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>137109567</v>
       </c>
       <c r="B22" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 38056-2026 artfynd.xlsx
+++ b/artfynd/A 38056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137103122</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137097664</v>
       </c>
       <c r="B3" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137098614</v>
       </c>
       <c r="B4" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137098702</v>
       </c>
       <c r="B5" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137101340</v>
       </c>
       <c r="B6" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137101898</v>
       </c>
       <c r="B7" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137102625</v>
       </c>
       <c r="B8" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137109725</v>
       </c>
       <c r="B9" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>137097652</v>
       </c>
       <c r="B10" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>137119497</v>
       </c>
       <c r="B11" t="n">
-        <v>92596</v>
+        <v>92600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>137101121</v>
       </c>
       <c r="B12" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>137101232</v>
       </c>
       <c r="B13" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137101624</v>
       </c>
       <c r="B14" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137101158</v>
       </c>
       <c r="B15" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>137102567</v>
       </c>
       <c r="B16" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>137109598</v>
       </c>
       <c r="B17" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>137109858</v>
       </c>
       <c r="B18" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>137109552</v>
       </c>
       <c r="B21" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>137109567</v>
       </c>
       <c r="B22" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>137119393</v>
       </c>
       <c r="B27" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>137119536</v>
       </c>
       <c r="B28" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>137119430</v>
       </c>
       <c r="B29" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
